--- a/results_analysis_monteprep.xlsx
+++ b/results_analysis_monteprep.xlsx
@@ -429,10 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.012873</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>7604.86</v>
+        <v>822.58</v>
       </c>
     </row>
     <row r="4">
@@ -663,16 +663,16 @@
         <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4684</v>
+        <v>0.7342</v>
       </c>
       <c r="H6" t="n">
-        <v>0.042338</v>
+        <v>0.058814</v>
       </c>
       <c r="I6" t="n">
-        <v>750.26</v>
+        <v>770.35</v>
       </c>
     </row>
     <row r="7">
@@ -771,25 +771,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.042471</v>
+      </c>
+      <c r="I9" t="n">
+        <v>156.28</v>
       </c>
     </row>
     <row r="10">
@@ -888,19 +882,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>0.641</v>
+        <v>0.575</v>
       </c>
       <c r="H12" t="n">
-        <v>0.118711</v>
+        <v>0.123943</v>
       </c>
       <c r="I12" t="n">
-        <v>112.56</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="13">
@@ -999,25 +993,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.032199</v>
+      </c>
+      <c r="I15" t="n">
+        <v>133.54</v>
       </c>
     </row>
     <row r="16">
@@ -1116,25 +1104,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.114516</v>
+      </c>
+      <c r="I18" t="n">
+        <v>149.55</v>
       </c>
     </row>
     <row r="19">
@@ -1233,25 +1215,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.023862</v>
+      </c>
+      <c r="I21" t="n">
+        <v>145.81</v>
       </c>
     </row>
     <row r="22">
@@ -1350,25 +1326,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.080552</v>
+      </c>
+      <c r="I24" t="n">
+        <v>172.12</v>
       </c>
     </row>
     <row r="25">
@@ -1406,6 +1376,228 @@
       </c>
       <c r="I25" t="n">
         <v>303.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>99</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.005428</v>
+      </c>
+      <c r="I26" t="n">
+        <v>28.19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.001546</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>29</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="I28" t="n">
+        <v>17.56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>99</v>
+      </c>
+      <c r="F29" t="n">
+        <v>72</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.027336</v>
+      </c>
+      <c r="I29" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.016645</v>
+      </c>
+      <c r="I30" t="n">
+        <v>18.71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.024224</v>
+      </c>
+      <c r="I31" t="n">
+        <v>26.85</v>
       </c>
     </row>
   </sheetData>
@@ -1419,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1623,8 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1479,6 +1673,16 @@
           <t>MCTS (o4-mini)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1510,6 +1714,12 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1541,6 +1751,12 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1572,6 +1788,12 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1603,6 +1825,12 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1634,6 +1862,12 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1665,6 +1899,12 @@
       <c r="I7" t="n">
         <v>1</v>
       </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1696,6 +1936,12 @@
       <c r="I8" t="n">
         <v>1</v>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1727,6 +1973,12 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1758,6 +2010,12 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1789,6 +2047,12 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1820,6 +2084,12 @@
       <c r="I12" t="n">
         <v>1</v>
       </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1851,6 +2121,12 @@
       <c r="I13" t="n">
         <v>1</v>
       </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1882,6 +2158,12 @@
       <c r="I14" t="n">
         <v>1</v>
       </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1913,6 +2195,12 @@
       <c r="I15" t="n">
         <v>1</v>
       </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1944,6 +2232,12 @@
       <c r="I16" t="n">
         <v>1</v>
       </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1975,6 +2269,12 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2006,6 +2306,12 @@
       <c r="I18" t="n">
         <v>1</v>
       </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2037,6 +2343,12 @@
       <c r="I19" t="n">
         <v>1</v>
       </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2068,6 +2380,12 @@
       <c r="I20" t="n">
         <v>1</v>
       </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2099,6 +2417,12 @@
       <c r="I21" t="n">
         <v>1</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2130,6 +2454,12 @@
       <c r="I22" t="n">
         <v>1</v>
       </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2161,6 +2491,12 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2192,6 +2528,12 @@
       <c r="I24" t="n">
         <v>1</v>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2223,6 +2565,12 @@
       <c r="I25" t="n">
         <v>1</v>
       </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2254,6 +2602,12 @@
       <c r="I26" t="n">
         <v>1</v>
       </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2285,6 +2639,12 @@
       <c r="I27" t="n">
         <v>1</v>
       </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2316,6 +2676,12 @@
       <c r="I28" t="n">
         <v>1</v>
       </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2347,6 +2713,12 @@
       <c r="I29" t="n">
         <v>1</v>
       </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2378,6 +2750,12 @@
       <c r="I30" t="n">
         <v>1</v>
       </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2409,6 +2787,12 @@
       <c r="I31" t="n">
         <v>1</v>
       </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2440,6 +2824,12 @@
       <c r="I32" t="n">
         <v>1</v>
       </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2471,6 +2861,12 @@
       <c r="I33" t="n">
         <v>1</v>
       </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2502,6 +2898,12 @@
       <c r="I34" t="n">
         <v>1</v>
       </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2533,6 +2935,12 @@
       <c r="I35" t="n">
         <v>1</v>
       </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2564,6 +2972,12 @@
       <c r="I36" t="n">
         <v>1</v>
       </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2595,6 +3009,12 @@
       <c r="I37" t="n">
         <v>1</v>
       </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2626,6 +3046,12 @@
       <c r="I38" t="n">
         <v>1</v>
       </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2657,6 +3083,12 @@
       <c r="I39" t="n">
         <v>1</v>
       </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2688,6 +3120,12 @@
       <c r="I40" t="n">
         <v>1</v>
       </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2719,6 +3157,12 @@
       <c r="I41" t="n">
         <v>1</v>
       </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2750,6 +3194,12 @@
       <c r="I42" t="n">
         <v>1</v>
       </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2781,6 +3231,12 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2812,6 +3268,12 @@
       <c r="I44" t="n">
         <v>1</v>
       </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2843,6 +3305,12 @@
       <c r="I45" t="n">
         <v>1</v>
       </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2874,6 +3342,12 @@
       <c r="I46" t="n">
         <v>1</v>
       </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2905,6 +3379,12 @@
       <c r="I47" t="n">
         <v>1</v>
       </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2936,6 +3416,12 @@
       <c r="I48" t="n">
         <v>1</v>
       </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2967,6 +3453,12 @@
       <c r="I49" t="n">
         <v>1</v>
       </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2998,6 +3490,12 @@
       <c r="I50" t="n">
         <v>1</v>
       </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3029,6 +3527,12 @@
       <c r="I51" t="n">
         <v>1</v>
       </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3060,6 +3564,12 @@
       <c r="I52" t="n">
         <v>1</v>
       </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3091,6 +3601,12 @@
       <c r="I53" t="n">
         <v>1</v>
       </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3122,6 +3638,12 @@
       <c r="I54" t="n">
         <v>1</v>
       </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3153,6 +3675,12 @@
       <c r="I55" t="n">
         <v>1</v>
       </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3184,6 +3712,12 @@
       <c r="I56" t="n">
         <v>1</v>
       </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3215,6 +3749,12 @@
       <c r="I57" t="n">
         <v>1</v>
       </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3246,6 +3786,12 @@
       <c r="I58" t="n">
         <v>1</v>
       </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3277,6 +3823,12 @@
       <c r="I59" t="n">
         <v>1</v>
       </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3308,6 +3860,12 @@
       <c r="I60" t="n">
         <v>1</v>
       </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3339,6 +3897,12 @@
       <c r="I61" t="n">
         <v>1</v>
       </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3370,6 +3934,12 @@
       <c r="I62" t="n">
         <v>1</v>
       </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3401,6 +3971,12 @@
       <c r="I63" t="n">
         <v>1</v>
       </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3432,6 +4008,12 @@
       <c r="I64" t="n">
         <v>1</v>
       </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3463,6 +4045,12 @@
       <c r="I65" t="n">
         <v>1</v>
       </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3494,6 +4082,12 @@
       <c r="I66" t="n">
         <v>1</v>
       </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3525,6 +4119,12 @@
       <c r="I67" t="n">
         <v>1</v>
       </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3556,6 +4156,12 @@
       <c r="I68" t="n">
         <v>1</v>
       </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3587,6 +4193,12 @@
       <c r="I69" t="n">
         <v>1</v>
       </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3618,6 +4230,12 @@
       <c r="I70" t="n">
         <v>1</v>
       </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3649,6 +4267,12 @@
       <c r="I71" t="n">
         <v>1</v>
       </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3680,6 +4304,12 @@
       <c r="I72" t="n">
         <v>1</v>
       </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3711,6 +4341,12 @@
       <c r="I73" t="n">
         <v>1</v>
       </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3742,6 +4378,12 @@
       <c r="I74" t="n">
         <v>1</v>
       </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3773,6 +4415,12 @@
       <c r="I75" t="n">
         <v>1</v>
       </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3804,6 +4452,12 @@
       <c r="I76" t="n">
         <v>1</v>
       </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3835,6 +4489,12 @@
       <c r="I77" t="n">
         <v>1</v>
       </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3866,6 +4526,12 @@
       <c r="I78" t="n">
         <v>1</v>
       </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3897,6 +4563,12 @@
       <c r="I79" t="n">
         <v>1</v>
       </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3928,6 +4600,12 @@
       <c r="I80" t="n">
         <v>1</v>
       </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3959,6 +4637,12 @@
       <c r="I81" t="n">
         <v>1</v>
       </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3990,6 +4674,12 @@
       <c r="I82" t="n">
         <v>1</v>
       </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4021,6 +4711,12 @@
       <c r="I83" t="n">
         <v>1</v>
       </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4052,6 +4748,12 @@
       <c r="I84" t="n">
         <v>1</v>
       </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4083,6 +4785,12 @@
       <c r="I85" t="n">
         <v>1</v>
       </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4114,6 +4822,12 @@
       <c r="I86" t="n">
         <v>1</v>
       </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4145,6 +4859,12 @@
       <c r="I87" t="n">
         <v>1</v>
       </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4176,6 +4896,12 @@
       <c r="I88" t="n">
         <v>1</v>
       </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4207,6 +4933,12 @@
       <c r="I89" t="n">
         <v>0</v>
       </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4238,6 +4970,12 @@
       <c r="I90" t="n">
         <v>1</v>
       </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4269,6 +5007,12 @@
       <c r="I91" t="n">
         <v>0</v>
       </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4300,6 +5044,12 @@
       <c r="I92" t="n">
         <v>1</v>
       </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4331,6 +5081,12 @@
       <c r="I93" t="n">
         <v>1</v>
       </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4362,6 +5118,12 @@
       <c r="I94" t="n">
         <v>1</v>
       </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4393,6 +5155,12 @@
       <c r="I95" t="n">
         <v>1</v>
       </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4424,6 +5192,16 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4455,6 +5233,12 @@
       <c r="I97" t="n">
         <v>1</v>
       </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4486,6 +5270,12 @@
       <c r="I98" t="n">
         <v>1</v>
       </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4517,6 +5307,12 @@
       <c r="I99" t="n">
         <v>1</v>
       </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4548,6 +5344,12 @@
       <c r="I100" t="n">
         <v>1</v>
       </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4577,6 +5379,12 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4591,13 +5399,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4618,7 +5433,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>AF Operator (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>AF Operator (o4-mini)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AF Pipeline (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AF Pipeline (o4-mini)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
         </is>
       </c>
     </row>
@@ -4641,6 +5491,27 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4657,6 +5528,27 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4673,6 +5565,27 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4686,10 +5599,29 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4704,10 +5636,29 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4722,10 +5673,29 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4740,10 +5710,29 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4758,10 +5747,29 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4776,10 +5784,29 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4788,18 +5815,35 @@
           <t>4_9</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4808,15 +5852,34 @@
           <t>4_10</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4826,16 +5889,35 @@
           <t>4_11</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4844,16 +5926,35 @@
           <t>4_12</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B14" t="n">
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4862,15 +5963,34 @@
           <t>4_13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B15" t="n">
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4880,15 +6000,34 @@
           <t>4_14</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B16" t="n">
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4898,15 +6037,34 @@
           <t>4_15</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B17" t="n">
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4916,16 +6074,35 @@
           <t>4_16</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4934,15 +6111,34 @@
           <t>4_17</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B19" t="n">
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4952,15 +6148,34 @@
           <t>4_18</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4970,15 +6185,34 @@
           <t>4_19</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4988,15 +6222,34 @@
           <t>4_20</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5014,10 +6267,29 @@
       <c r="C23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -5026,18 +6298,35 @@
           <t>4_22</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -5046,18 +6335,35 @@
           <t>4_23</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B25" t="n">
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -5066,18 +6372,35 @@
           <t>4_24</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -5086,18 +6409,35 @@
           <t>4_25</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -5106,18 +6446,35 @@
           <t>4_26</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -5126,18 +6483,35 @@
           <t>4_27</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -5146,18 +6520,35 @@
           <t>4_28</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5166,18 +6557,35 @@
           <t>4_29</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -5186,18 +6594,35 @@
           <t>4_30</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B32" t="n">
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5206,18 +6631,35 @@
           <t>4_31</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B33" t="n">
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5226,18 +6668,35 @@
           <t>4_32</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -5246,18 +6705,35 @@
           <t>4_33</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -5266,18 +6742,35 @@
           <t>4_34</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B36" t="n">
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -5286,18 +6779,35 @@
           <t>4_35</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B37" t="n">
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -5306,18 +6816,35 @@
           <t>4_36</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B38" t="n">
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5326,18 +6853,35 @@
           <t>4_37</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B39" t="n">
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -5346,18 +6890,35 @@
           <t>4_38</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B40" t="n">
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5366,18 +6927,35 @@
           <t>4_39</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B41" t="n">
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -5386,16 +6964,35 @@
           <t>4_40</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B42" t="n">
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5404,15 +7001,34 @@
           <t>4_41</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B43" t="n">
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5422,15 +7038,34 @@
           <t>4_42</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B44" t="n">
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5440,16 +7075,35 @@
           <t>4_43</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B45" t="n">
+        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5458,15 +7112,34 @@
           <t>4_44</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B46" t="n">
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5476,16 +7149,35 @@
           <t>4_45</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B47" t="n">
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5494,15 +7186,34 @@
           <t>4_46</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B48" t="n">
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5512,16 +7223,35 @@
           <t>4_47</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B49" t="n">
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5530,15 +7260,34 @@
           <t>4_48</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B50" t="n">
+        <v>1</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5548,15 +7297,34 @@
           <t>4_49</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B51" t="n">
+        <v>1</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5566,15 +7334,34 @@
           <t>4_50</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B52" t="n">
+        <v>1</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5584,15 +7371,34 @@
           <t>4_51</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B53" t="n">
+        <v>1</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5602,15 +7408,34 @@
           <t>4_52</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B54" t="n">
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5620,15 +7445,34 @@
           <t>4_53</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B55" t="n">
+        <v>1</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5638,16 +7482,35 @@
           <t>4_54</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B56" t="n">
+        <v>1</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5656,15 +7519,34 @@
           <t>4_55</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B57" t="n">
+        <v>1</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5674,15 +7556,34 @@
           <t>4_56</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B58" t="n">
+        <v>1</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5692,15 +7593,34 @@
           <t>4_57</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B59" t="n">
+        <v>1</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5710,15 +7630,34 @@
           <t>4_58</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B60" t="n">
+        <v>1</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5728,15 +7667,34 @@
           <t>4_59</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B61" t="n">
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5746,15 +7704,34 @@
           <t>4_60</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B62" t="n">
+        <v>1</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5764,15 +7741,34 @@
           <t>4_61</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B63" t="n">
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5782,16 +7778,35 @@
           <t>4_62</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B64" t="n">
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5800,16 +7815,35 @@
           <t>4_63</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B65" t="n">
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5818,15 +7852,34 @@
           <t>4_64</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B66" t="n">
+        <v>1</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5836,18 +7889,35 @@
           <t>4_65</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B67" t="n">
+        <v>1</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -5856,18 +7926,35 @@
           <t>4_66</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B68" t="n">
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -5876,18 +7963,35 @@
           <t>4_67</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B69" t="n">
+        <v>1</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5896,18 +8000,35 @@
           <t>4_68</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B70" t="n">
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5916,18 +8037,35 @@
           <t>4_69</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B71" t="n">
+        <v>0</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5936,18 +8074,35 @@
           <t>4_70</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B72" t="n">
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -5956,18 +8111,35 @@
           <t>4_71</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B73" t="n">
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -5976,18 +8148,35 @@
           <t>4_72</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -5996,18 +8185,35 @@
           <t>4_73</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B75" t="n">
+        <v>1</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6016,18 +8222,35 @@
           <t>4_74</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B76" t="n">
+        <v>1</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6036,18 +8259,35 @@
           <t>4_75</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B77" t="n">
+        <v>0</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6056,18 +8296,35 @@
           <t>4_76</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B78" t="n">
+        <v>1</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6076,18 +8333,35 @@
           <t>4_77</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B79" t="n">
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -6096,18 +8370,35 @@
           <t>4_78</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B80" t="n">
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -6116,18 +8407,35 @@
           <t>4_79</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B81" t="n">
+        <v>1</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6141,7 +8449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6153,6 +8461,8 @@
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6201,6 +8511,16 @@
           <t>MCTS (o4-mini)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6232,6 +8552,12 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6263,6 +8589,12 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6294,6 +8626,12 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6325,6 +8663,12 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6356,6 +8700,12 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6387,6 +8737,12 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6418,6 +8774,12 @@
       <c r="I8" t="n">
         <v>1</v>
       </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6453,6 +8815,12 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6484,6 +8852,16 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6515,6 +8893,12 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6546,6 +8930,12 @@
       <c r="I12" t="n">
         <v>1</v>
       </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6577,6 +8967,12 @@
       <c r="I13" t="n">
         <v>1</v>
       </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6608,6 +9004,12 @@
       <c r="I14" t="n">
         <v>1</v>
       </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6639,6 +9041,12 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6670,6 +9078,12 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6701,6 +9115,12 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6732,6 +9152,12 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6763,6 +9189,12 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6794,6 +9226,12 @@
       <c r="I20" t="n">
         <v>1</v>
       </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6825,6 +9263,12 @@
       <c r="I21" t="n">
         <v>1</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6856,6 +9300,12 @@
       <c r="I22" t="n">
         <v>1</v>
       </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6887,6 +9337,12 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6918,6 +9374,12 @@
       <c r="I24" t="n">
         <v>1</v>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6949,6 +9411,12 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6980,6 +9448,12 @@
       <c r="I26" t="n">
         <v>1</v>
       </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7011,6 +9485,12 @@
       <c r="I27" t="n">
         <v>1</v>
       </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7042,6 +9522,12 @@
       <c r="I28" t="n">
         <v>1</v>
       </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7073,6 +9559,12 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7112,6 +9604,12 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7145,6 +9643,12 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7159,18 +9663,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7282,10 +9786,10 @@
         <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7294,7 +9798,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
+          <t>[0, 21]</t>
         </is>
       </c>
     </row>
@@ -7520,21 +10024,17 @@
         <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>✗ Not started</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7639,21 +10139,17 @@
         <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>⚠ Partial</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[3, 4, 5, 6, 7, 8, 9, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7758,21 +10254,17 @@
         <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>✗ Not started</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7873,21 +10365,17 @@
         <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>✗ Not started</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7988,21 +10476,17 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>✗ Not started</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8103,21 +10587,17 @@
         <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>✗ Not started</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8155,6 +10635,244 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="n">
+        <v>99</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[94]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F27" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (4.1-mini)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gpt-4.1-mini</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>30</v>
+      </c>
+      <c r="F28" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>99</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[94]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>o4-mini</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MontePrep MCTS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[8]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
